--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -574,6 +574,23 @@
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>회피 사용 시 신경 가속 모드에 들어갑니다. {0}초 동안 이동 속도가 {1} 증가합니다. (쿨타임 {2}초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UE_LightSaber</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>광자 가속</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>기본 공격 시 {0}초간 공격 속도가 {1}% 증가합니다. (최대 {2}스택)</t>
         </is>
       </c>
     </row>
@@ -588,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -729,6 +746,23 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>Using dodge activates Neural Acceleration Mode. Movement speed increases by {1} for {0} seconds. (Cooldown: {2}s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UE_LightSaber</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Photon Acceleration</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>On basic attack, attack speed increases by {1}% for {0} seconds. (Max {2} stacks)</t>
         </is>
       </c>
     </row>
@@ -743,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -884,6 +918,23 @@
       <c r="C8" t="inlineStr">
         <is>
           <t>回避使用時、神経加速モードに入ります。{0}秒間移動速度が{1}増加します。(クールタイム{2}秒)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UE_LightSaber</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>光子加速</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>通常攻撃時、{0}秒間攻撃速度が{1}%増加します。(最大{2}スタック)</t>
         </is>
       </c>
     </row>
@@ -898,7 +949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1042,6 +1093,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UE_LightSaber</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>光子加速</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>普通攻击时，{0}秒内攻击速度增加{1}%。(最多{2}层)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="R17d381e210ca4803"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="R68ea62d50cf94ec6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R330d070defa0455a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="R5878ef0dd2344e92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="R1ccc6ee94211460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="R3c85cb76b7fb45c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R6d026e1f0c2b42d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="R3d93543a3e0e4f8d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1007,6 +1007,94 @@
         <x:v>회피 사용 시 {0}초간 스킬 쿨타임이 {1}% 감소하고 이동 속도가 {2}% 증가합니다. (쿨타임 {3}초)</x:v>
       </x:c>
     </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>UE_VoidBarrage</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>공허 과압</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>체력이 {0}% 이하일 때 공격력이 {1}%, 공격 속도가 {2}% 증가합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>UE_GoldenTwinStar</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>황금 반동</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>치명타 적중 시 {0}초간 공격력이 {1}%, 치명타 확률이 {2}% 증가합니다. (쿨타임 {3}초)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>UE_MagmaCrusher</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>용융 외피</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>장착 중 공격력이 {0}%, 화염 피해 보너스가 {1} 증가하지만 방어력이 {2}% 감소합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>UE_ThunderCoil</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>연쇄 충전</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>적 처치 시 {0}초간 공격 속도가 {1}%, 전기 피해 보너스가 {2} 증가합니다. (쿨타임 {3}초)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>UE_IonCascade</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>이온 순환</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>장착 중 공격 속도가 {0}%, 전기 피해 보너스가 {1} 증가합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>UE_ArcVector</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>벡터 가속</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>치명타 적중 시 {0}초간 공격 속도가 {1}%, 치명타 확률이 {2}% 증가합니다. (쿨타임 {3}초)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>UE_BlueHorizon</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>수평선 너머</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>장착 중 전기 피해 보너스가 {0}, 치명타 확률이 {1}% 증가합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>UE_RedSingularity</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>특이점 붕괴</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>적 처치 시 {0}초간 공격력이 {1}% 증가하고 관통력이 {2} 증가합니다. (쿨타임 {3}초)</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1417,6 +1505,94 @@
         <x:v>On dodging, skill cooldowns decrease by {1}% and Move Speed increases by {2}% for {0} seconds. (Cooldown: {3}s)</x:v>
       </x:c>
     </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>UE_VoidBarrage</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>Void Overpressure</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>While HP is {0}% or lower, Attack increases by {1}% and Attack Speed by {2}%.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>UE_GoldenTwinStar</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>Golden Recoil</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>On a critical hit, Attack increases by {1}% and Critical Rate by {2}% for {0} seconds. (Cooldown: {3}s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>UE_MagmaCrusher</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>Molten Shell</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>While equipped, Attack increases by {0}% and Fire damage bonus by {1}, but Defense decreases by {2}%.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>UE_ThunderCoil</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>Chain Charge</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>On defeating an enemy, Attack Speed increases by {1}% and Electric damage bonus by {2} for {0} seconds. (Cooldown: {3}s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>UE_IonCascade</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>Ion Circulation</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>While equipped, Attack Speed increases by {0}% and Electric damage bonus by {1}.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>UE_ArcVector</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>Vector Acceleration</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>On a critical hit, Attack Speed increases by {1}% and Critical Rate by {2}% for {0} seconds. (Cooldown: {3}s)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>UE_BlueHorizon</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Beyond the Horizon</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>While equipped, Electric damage bonus increases by {0} and Critical Rate by {1}%.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>UE_RedSingularity</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>Singularity Collapse</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>On defeating an enemy, Attack increases by {1}% and Penetration by {2} for {0} seconds. (Cooldown: {3}s)</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1827,6 +2003,94 @@
         <x:v>回避時、{0}秒間スキルのクールダウンが{1}%短縮され、移動速度が{2}%上昇します。（クールダウン：{3}秒）</x:v>
       </x:c>
     </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>UE_VoidBarrage</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>虚空過圧</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>HPが{0}%以下の間、攻撃力が{1}%、攻撃速度が{2}%上昇します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>UE_GoldenTwinStar</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>黄金反動</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>クリティカル命中時、{0}秒間攻撃力が{1}%、クリティカル率が{2}%上昇します。（クールダウン：{3}秒）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>UE_MagmaCrusher</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>溶融外殻</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>装備中、攻撃力が{0}%、炎ダメージボーナスが{1}上昇しますが、防御力が{2}%低下します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>UE_ThunderCoil</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>連鎖充電</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>敵を倒すと、{0}秒間攻撃速度が{1}%、電気ダメージボーナスが{2}上昇します。（クールダウン：{3}秒）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>UE_IonCascade</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>イオン循環</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>装備中、攻撃速度が{0}%、電気ダメージボーナスが{1}上昇します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>UE_ArcVector</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>ベクター加速</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>クリティカル命中時、{0}秒間攻撃速度が{1}%、クリティカル率が{2}%上昇します。（クールダウン：{3}秒）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>UE_BlueHorizon</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>地平線の彼方</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>装備中、電気ダメージボーナスが{0}、クリティカル率が{1}%上昇します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>UE_RedSingularity</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>特異点崩壊</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>敵を倒すと、{0}秒間攻撃力が{1}%上昇し、貫通力が{2}上昇します。（クールダウン：{3}秒）</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2237,6 +2501,94 @@
         <x:v>闪避时，技能冷却缩短{1}%，移动速度提高{2}%，持续{0}秒。（冷却：{3}秒）</x:v>
       </x:c>
     </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>UE_VoidBarrage</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>虚空过压</x:v>
+      </x:c>
+      <x:c r="C37" t="str">
+        <x:v>生命值不高于{0}%时，攻击力提高{1}%，攻击速度提高{2}%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" t="str">
+        <x:v>UE_GoldenTwinStar</x:v>
+      </x:c>
+      <x:c r="B38" t="str">
+        <x:v>黄金后坐</x:v>
+      </x:c>
+      <x:c r="C38" t="str">
+        <x:v>暴击命中时，攻击力提高{1}%，暴击率提高{2}%，持续{0}秒。（冷却：{3}秒）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" t="str">
+        <x:v>UE_MagmaCrusher</x:v>
+      </x:c>
+      <x:c r="B39" t="str">
+        <x:v>熔融外壳</x:v>
+      </x:c>
+      <x:c r="C39" t="str">
+        <x:v>装备时，攻击力提高{0}%，火焰伤害加成提高{1}，但防御力降低{2}%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" t="str">
+        <x:v>UE_ThunderCoil</x:v>
+      </x:c>
+      <x:c r="B40" t="str">
+        <x:v>连锁充能</x:v>
+      </x:c>
+      <x:c r="C40" t="str">
+        <x:v>击败敌人时，攻击速度提高{1}%，电击伤害加成提高{2}，持续{0}秒。（冷却：{3}秒）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" t="str">
+        <x:v>UE_IonCascade</x:v>
+      </x:c>
+      <x:c r="B41" t="str">
+        <x:v>离子循环</x:v>
+      </x:c>
+      <x:c r="C41" t="str">
+        <x:v>装备时，攻击速度提高{0}%，电击伤害加成提高{1}。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" t="str">
+        <x:v>UE_ArcVector</x:v>
+      </x:c>
+      <x:c r="B42" t="str">
+        <x:v>矢量加速</x:v>
+      </x:c>
+      <x:c r="C42" t="str">
+        <x:v>暴击命中时，攻击速度提高{1}%，暴击率提高{2}%，持续{0}秒。（冷却：{3}秒）</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="str">
+        <x:v>UE_BlueHorizon</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>地平线之外</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>装备时，电击伤害加成提高{0}，暴击率提高{1}%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" t="str">
+        <x:v>UE_RedSingularity</x:v>
+      </x:c>
+      <x:c r="B44" t="str">
+        <x:v>奇点坍缩</x:v>
+      </x:c>
+      <x:c r="C44" t="str">
+        <x:v>击败敌人时，攻击力提高{1}%，穿透提高{2}，持续{0}秒。（冷却：{3}秒）</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="R1ccc6ee94211460d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="R3c85cb76b7fb45c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R6d026e1f0c2b42d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="R3d93543a3e0e4f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" r:id="R785ea58f47e1492a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" r:id="R5b964b57137b4b50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" r:id="R8ea88be7620c4023"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" r:id="Rddddecd20e214602"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1095,6 +1095,61 @@
         <x:v>적 처치 시 {0}초간 공격력이 {1}% 증가하고 관통력이 {2} 증가합니다. (쿨타임 {3}초)</x:v>
       </x:c>
     </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>UE_PhaseOrchid</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>허공 개화</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>장착 중 치명타 확률이 {0}, 스킬 범위가 {1}% 증가합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>UE_GlassCannon</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>유리 심장</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>장착 중 공격력이 {0}% 증가하지만 방어력이 {1}% 감소합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>UE_Incinerator</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>소각 압력</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>장착 중 공격력이 {0}%, 화염 피해 보너스가 {1} 증가하지만 방어력이 {2}% 감소합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>UE_Apocalypse</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>최후의 봉인</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>체력이 {0}% 이하일 때 공격력이 {1}%, 관통력이 {2} 증가합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>UE_ConversationStarter</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>반론 차단</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>피격 시 {0}초간 공격 속도가 {1}%, 방어력이 {2}% 증가합니다. (쿨타임 {3}초)</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1593,6 +1648,61 @@
         <x:v>On defeating an enemy, Attack increases by {1}% and Penetration by {2} for {0} seconds. (Cooldown: {3}s)</x:v>
       </x:c>
     </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>UE_PhaseOrchid</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>Void Bloom</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>While equipped, Critical Hit Chance increases by {0} and Skill Range by {1}%.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>UE_GlassCannon</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>Glass Heart</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>While equipped, Attack Power increases by {0}%, but Defense decreases by {1}%.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>UE_Incinerator</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>Incineration Pressure</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>While equipped, Attack Power increases by {0}% and Fire Damage Bonus by {1}, but Defense decreases by {2}%.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>UE_Apocalypse</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>Final Seal</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>While Health is at or below {0}%, Attack Power increases by {1}% and Penetration by {2}.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>UE_ConversationStarter</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>Rebuttal Denied</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>When hit, Attack Speed increases by {1}% and Defense by {2}% for {0} seconds. (Cooldown: {3} seconds)</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2091,6 +2201,61 @@
         <x:v>敵を倒すと、{0}秒間攻撃力が{1}%上昇し、貫通力が{2}上昇します。（クールダウン：{3}秒）</x:v>
       </x:c>
     </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>UE_PhaseOrchid</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>虚空開花</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>装備中、クリティカル率が{0}、スキル範囲が{1}%増加します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>UE_GlassCannon</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>硝子の心臓</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>装備中、攻撃力が{0}%増加する代わりに、防御力が{1}%減少します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>UE_Incinerator</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>焼却圧力</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>装備中、攻撃力が{0}%、炎属性ダメージボーナスが{1}増加する代わりに、防御力が{2}%減少します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>UE_Apocalypse</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>最後の封印</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>体力が{0}%以下の間、攻撃力が{1}%、貫通力が{2}増加します。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>UE_ConversationStarter</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>反論封鎖</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>被弾時、{0}秒間、攻撃速度が{1}%、防御力が{2}%増加します。（クールタイム{3}秒）</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2589,6 +2754,61 @@
         <x:v>击败敌人时，攻击力提高{1}%，穿透提高{2}，持续{0}秒。（冷却：{3}秒）</x:v>
       </x:c>
     </x:row>
+    <x:row r="45">
+      <x:c r="A45" t="str">
+        <x:v>UE_PhaseOrchid</x:v>
+      </x:c>
+      <x:c r="B45" t="str">
+        <x:v>虚空绽放</x:v>
+      </x:c>
+      <x:c r="C45" t="str">
+        <x:v>装备期间，暴击率提高{0}，技能范围提高{1}%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" t="str">
+        <x:v>UE_GlassCannon</x:v>
+      </x:c>
+      <x:c r="B46" t="str">
+        <x:v>玻璃之心</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>装备期间，攻击力提高{0}%，但防御力降低{1}%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" t="str">
+        <x:v>UE_Incinerator</x:v>
+      </x:c>
+      <x:c r="B47" t="str">
+        <x:v>焚化压力</x:v>
+      </x:c>
+      <x:c r="C47" t="str">
+        <x:v>装备期间，攻击力提高{0}%，火焰伤害加成提高{1}，但防御力降低{2}%。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>UE_Apocalypse</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>最终封印</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>生命值不高于{0}%时，攻击力提高{1}%，穿透力提高{2}。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>UE_ConversationStarter</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>驳回反论</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>受到攻击时，攻击速度提高{1}%，防御力提高{2}%，持续{0}秒。（冷却时间{3}秒）</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -1652,7 +1652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2232,6 +2232,40 @@
         <v>445</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_DodgeMoveBoost</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔여 추력</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회피 사용 후 {0}초간 일반 이동 속도가 {1}% 증가합니다. (쿨타임 {2}초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_ManaRelay</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마나 중계</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반경 {0}m 안의 자신과 살아 있는 아군의 마나 재생이 {1}% 증가합니다. 같은 효과는 중첩되지 않습니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2240,7 +2274,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -2820,6 +2854,40 @@
         <v>447</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_DodgeMoveBoost</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residual Thrust</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">After using dodge, normal movement speed increases by {1}% for {0} seconds. Cooldown: {2} seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_ManaRelay</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mana Relay</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Increases mana regeneration of you and living allies within {0}m by {1}%. Does not stack with the same effect.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2828,7 +2896,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3408,6 +3476,40 @@
         <v>441</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_DodgeMoveBoost</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">残留推力</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">回避使用後{0}秒間、通常移動速度が{1}%増加します。クールタイム：{2}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_ManaRelay</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">マナ中継</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径{0}m以内の自分と生存中の味方のマナ回復が{1}%増加します。同じ効果は重複しません。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3416,7 +3518,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -3996,6 +4098,40 @@
         <v>443</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_DodgeMoveBoost</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">残余推力</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">使用闪避后，普通移动速度提高{1}%，持续{0}秒。冷却时间：{2}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_ManaRelay</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">法力中继</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">自身和半径{0}米内存活队友的法力恢复提高{1}%。同类效果不叠加。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -59,10 +59,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -361,7 +373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1845,6 +1857,23 @@
       <c r="C87" t="inlineStr">
         <is>
           <t>장착 중 공격 속도가 {0}% 증가하지만 최대 체력이 {1}% 감소합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="88" ht="26.399999618530273" customHeight="1">
+      <c r="A88" t="inlineStr" s="4">
+        <is>
+          <t>UE_PhaseHarvesterWave</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="4">
+        <is>
+          <t>공허 처형 파동</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="5">
+        <is>
+          <t>Fighter 기본 공격 처치 시 그 위치에서 전방 {0}m, 폭 {1}m의 처형 파동을 방출합니다. 최대 {3}체에 치명타 없는 무속성 피해 {2}%를 한 번 줍니다. 재사용 대기시간 {4}초.</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3343,6 +3372,23 @@
       <c r="C87" t="inlineStr">
         <is>
           <t>While equipped, Attack Speed increases by {0}%, but max HP decreases by {1}%.</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="88" ht="52.79999923706055" customHeight="1">
+      <c r="A88" t="inlineStr" s="4">
+        <is>
+          <t>UE_PhaseHarvesterWave</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="4">
+        <is>
+          <t>Void Execution Wave</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="5">
+        <is>
+          <t>When a Fighter basic attack kills an enemy, an execution wave instantly covers a {0}m-long, {1}m-wide corridor ahead of the kill position. It deals {2}% non-elemental damage once to up to {3} living enemies, without critical hits or repeated activation. Cooldown: {4}s.</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4841,6 +4887,23 @@
       <c r="C87" t="inlineStr">
         <is>
           <t>装備中、攻撃速度が{0}%上昇しますが、最大HPが{1}%低下します。</t>
+        </is>
+      </c>
+    </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="88" ht="39.599998474121094" customHeight="1">
+      <c r="A88" t="inlineStr" s="4">
+        <is>
+          <t>UE_PhaseHarvesterWave</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="4">
+        <is>
+          <t>虚空の処刑波</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="5">
+        <is>
+          <t>ファイターの通常攻撃で敵を倒すと、その位置から前方{0}m、幅{1}mの処刑波が即座に発生します。生存する最大{3}体に無属性ダメージ{2}%を1回与えます。クリティカルや連鎖発動は発生しません。クールダウンは{4}秒です。</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6342,6 +6405,23 @@
         </is>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="88" ht="39.599998474121094" customHeight="1">
+      <c r="A88" t="inlineStr" s="4">
+        <is>
+          <t>UE_PhaseHarvesterWave</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr" s="4">
+        <is>
+          <t>虚空处决波</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr" s="5">
+        <is>
+          <t>斗士普通攻击击杀敌人后，立即从击杀位置向前形成长{0}米、宽{1}米的处决通道。对最多{3}个存活敌人各造成一次{2}%无属性伤害，不会暴击或连锁触发。冷却时间为{4}秒。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -373,7 +373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1875,6 +1875,17 @@
         <is>
           <t>Fighter 기본 공격 처치 시 그 위치에서 전방 {0}m, 폭 {1}m의 처형 파동을 방출합니다. 최대 {3}체에 치명타 없는 무속성 피해 {2}%를 한 번 줍니다. 재사용 대기시간 {4}초.</t>
         </is>
+      </c>
+    </row>
+    <row r="89" ht="26.399999618530273" customHeight="1">
+      <c r="A89" t="str" s="4">
+        <v>UE_StarforgeBreachExplosion</v>
+      </c>
+      <c r="B89" t="str" s="6">
+        <v>스타 브리처 근접 폭발</v>
+      </c>
+      <c r="C89" s="5" t="str">
+        <v>거너 기본 산탄총 공격이 발사 원점에서 {0}m 이내의 적을 명중하면 그 피격 위치에 반경 {1}m 폭발을 일으킵니다. 최대 {3}체에 치명타 없는 화염 피해 {2}%를 한 번 줍니다. 재사용 대기시간 {4}초.</v>
       </c>
     </row>
   </sheetData>
@@ -1888,7 +1899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3390,6 +3401,17 @@
         <is>
           <t>When a Fighter basic attack kills an enemy, an execution wave instantly covers a {0}m-long, {1}m-wide corridor ahead of the kill position. It deals {2}% non-elemental damage once to up to {3} living enemies, without critical hits or repeated activation. Cooldown: {4}s.</t>
         </is>
+      </c>
+    </row>
+    <row r="89" ht="39.599998474121094" customHeight="1">
+      <c r="A89" t="str" s="4">
+        <v>UE_StarforgeBreachExplosion</v>
+      </c>
+      <c r="B89" t="str" s="6">
+        <v>Star Breacher Close-Range Explosion</v>
+      </c>
+      <c r="C89" s="5" t="str">
+        <v>A Gunner basic shotgun hit within {0}m of the firing origin causes an explosion of radius {1}m at the impact point. It deals {2}% Fire damage once to up to {3} enemies, without critical hits. Cooldown: {4}s.</v>
       </c>
     </row>
   </sheetData>
@@ -3403,7 +3425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4905,6 +4927,17 @@
         <is>
           <t>ファイターの通常攻撃で敵を倒すと、その位置から前方{0}m、幅{1}mの処刑波が即座に発生します。生存する最大{3}体に無属性ダメージ{2}%を1回与えます。クリティカルや連鎖発動は発生しません。クールダウンは{4}秒です。</t>
         </is>
+      </c>
+    </row>
+    <row r="89" ht="39.599998474121094" customHeight="1">
+      <c r="A89" t="str" s="4">
+        <v>UE_StarforgeBreachExplosion</v>
+      </c>
+      <c r="B89" t="str" s="6">
+        <v>スターブリーチャー近距離爆発</v>
+      </c>
+      <c r="C89" s="5" t="str">
+        <v>ガンナーの通常ショットガン攻撃が発射位置から{0}m以内の敵に命中すると、命中位置に半径{1}mの爆発を起こします。最大{3}体にクリティカルなしの火炎ダメージ{2}%を1回与えます。クールダウン：{4}秒。</v>
       </c>
     </row>
   </sheetData>
@@ -4918,7 +4951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6422,6 +6455,17 @@
         </is>
       </c>
     </row>
+    <row r="89" ht="26.399999618530273" customHeight="1">
+      <c r="A89" t="str" s="4">
+        <v>UE_StarforgeBreachExplosion</v>
+      </c>
+      <c r="B89" t="str" s="6">
+        <v>星辰破阵者近距离爆炸</v>
+      </c>
+      <c r="C89" s="5" t="str">
+        <v>枪手的普通霰弹枪攻击命中距发射位置{0}m以内的敌人时，在命中位置引发半径{1}m的爆炸。对最多{3}个敌人造成一次{2}%火焰伤害，不会暴击。冷却时间：{4}秒。</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -373,7 +373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1886,6 +1886,17 @@
       </c>
       <c r="C89" s="5" t="str">
         <v>거너 기본 산탄총 공격이 발사 원점에서 {0}m 이내의 적을 명중하면 그 피격 위치에 반경 {1}m 폭발을 일으킵니다. 최대 {3}체에 치명타 없는 화염 피해 {2}%를 한 번 줍니다. 재사용 대기시간 {4}초.</v>
+      </c>
+    </row>
+    <row r="90" ht="39.599998474121094" customHeight="1">
+      <c r="A90" s="4" t="str">
+        <v>UE_WasteHeatDischarge</v>
+      </c>
+      <c r="B90" s="6" t="str">
+        <v>폐열 방출</v>
+      </c>
+      <c r="C90" s="5" t="str">
+        <v>서로 다른 기본 공격이 적중할 때마다 열을 1씩 쌓아 최대 {0}까지 충전합니다. 충전 완료 후 다음 유효 기본 공격은 열을 모두 소비해 전방 {1}m·전체 각도 {2}° 범위의 적 최대 {4}체에게 공격력의 {3}%에 해당하는 치명타 없는 화염 피해를 추가로 줍니다. {5}초간 기본 공격이 적중하지 않으면 열이 사라집니다.</v>
       </c>
     </row>
   </sheetData>
@@ -1899,7 +1910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3412,6 +3423,17 @@
       </c>
       <c r="C89" s="5" t="str">
         <v>A Gunner basic shotgun hit within {0}m of the firing origin causes an explosion of radius {1}m at the impact point. It deals {2}% Fire damage once to up to {3} enemies, without critical hits. Cooldown: {4}s.</v>
+      </c>
+    </row>
+    <row r="90" ht="52.79999923706055" customHeight="1">
+      <c r="A90" s="4" t="str">
+        <v>UE_WasteHeatDischarge</v>
+      </c>
+      <c r="B90" s="6" t="str">
+        <v>Waste Heat Discharge</v>
+      </c>
+      <c r="C90" s="5" t="str">
+        <v>Each distinct basic attack that hits builds 1 Heat, up to {0}. Once fully charged, the next valid basic hit consumes all Heat and deals non-critical Fire damage equal to {3}% of Attack Power to up to {4} enemies in a {1}m frontal cone with a total angle of {2}°. Heat expires after {5}s without a basic hit.</v>
       </c>
     </row>
   </sheetData>
@@ -3425,7 +3447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4938,6 +4960,17 @@
       </c>
       <c r="C89" s="5" t="str">
         <v>ガンナーの通常ショットガン攻撃が発射位置から{0}m以内の敵に命中すると、命中位置に半径{1}mの爆発を起こします。最大{3}体にクリティカルなしの火炎ダメージ{2}%を1回与えます。クールダウン：{4}秒。</v>
+      </c>
+    </row>
+    <row r="90" ht="52.79999923706055" customHeight="1">
+      <c r="A90" s="4" t="str">
+        <v>UE_WasteHeatDischarge</v>
+      </c>
+      <c r="B90" s="6" t="str">
+        <v>廃熱放出</v>
+      </c>
+      <c r="C90" s="5" t="str">
+        <v>異なる通常攻撃が命中するたびに熱を1蓄積し、最大{0}までチャージします。チャージ完了後の次の有効な通常攻撃で熱をすべて消費し、前方{1}m・全角{2}°内の敵最大{4}体に攻撃力の{3}%のクリティカルなしの炎ダメージを追加で与えます。通常攻撃が{5}秒間命中しないと熱が消失します。</v>
       </c>
     </row>
   </sheetData>
@@ -4951,7 +4984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6466,6 +6499,17 @@
         <v>枪手的普通霰弹枪攻击命中距发射位置{0}m以内的敌人时，在命中位置引发半径{1}m的爆炸。对最多{3}个敌人造成一次{2}%火焰伤害，不会暴击。冷却时间：{4}秒。</v>
       </c>
     </row>
+    <row r="90" ht="39.599998474121094" customHeight="1">
+      <c r="A90" s="4" t="str">
+        <v>UE_WasteHeatDischarge</v>
+      </c>
+      <c r="B90" s="6" t="str">
+        <v>废热释放</v>
+      </c>
+      <c r="C90" s="5" t="str">
+        <v>每次不同的普通攻击命中时积累1点热量，最多{0}点。充满后，下次有效普通攻击消耗全部热量，对前方{1}米、总夹角{2}°内最多{4}个敌人额外造成攻击力{3}%的无法暴击的火焰伤害。{5}秒内没有普通攻击命中时，热量清空。</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -59,7 +59,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -76,6 +76,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -373,7 +376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1873,7 +1876,7 @@
       </c>
       <c r="C88" t="inlineStr" s="5">
         <is>
-          <t>Fighter 기본 공격 처치 시 그 위치에서 전방 {0}m, 폭 {1}m의 처형 파동을 방출합니다. 최대 {3}체에 치명타 없는 무속성 피해 {2}%를 한 번 줍니다. 재사용 대기시간 {4}초.</t>
+          <t>근접 기본 공격으로 처치 시 전방 {0}m·폭 {1}m의 파동을 방출합니다. 최대 {3}명에게 공격력의 {2}% 무속성 피해를 주며 치명타는 없습니다. (쿨타임 {4}초)</t>
         </is>
       </c>
     </row>
@@ -1884,8 +1887,10 @@
       <c r="B89" t="str" s="6">
         <v>스타 브리처 근접 폭발</v>
       </c>
-      <c r="C89" s="5" t="str">
-        <v>거너 기본 산탄총 공격이 발사 원점에서 {0}m 이내의 적을 명중하면 그 피격 위치에 반경 {1}m 폭발을 일으킵니다. 최대 {3}체에 치명타 없는 화염 피해 {2}%를 한 번 줍니다. 재사용 대기시간 {4}초.</v>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>{0}m 이내 산탄 적중 시 반경 {1}m에 폭발을 일으킵니다. 최대 {3}명에게 공격력의 {2}% 화염 피해를 주며 치명타는 없습니다. (쿨타임 {4}초)</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="39.599998474121094" customHeight="1">
@@ -1895,8 +1900,197 @@
       <c r="B90" s="6" t="str">
         <v>폐열 방출</v>
       </c>
-      <c r="C90" s="5" t="str">
-        <v>서로 다른 기본 공격이 적중할 때마다 열을 1씩 쌓아 최대 {0}까지 충전합니다. 충전 완료 후 다음 유효 기본 공격은 열을 모두 소비해 전방 {1}m·전체 각도 {2}° 범위의 적 최대 {4}체에게 공격력의 {3}%에 해당하는 치명타 없는 화염 피해를 추가로 줍니다. {5}초간 기본 공격이 적중하지 않으면 열이 사라집니다.</v>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>기본 공격 {0}회 적중 후 다음 적중 시 화염을 방출합니다. 전방 {1}m·{2}° 내 최대 {4}명에게 공격력의 {3}% 추가 피해를 줍니다. 치명타는 없으며 {5}초간 미적중 시 충전이 초기화됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="48" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>UE_SunfallBurnField</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>일식 점화</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>유탄 충돌 시 반경 {0}m에 {1}초간 화상 지대를 남깁니다. {2}초마다 화상을 갱신하며 최대 {3}개까지 유지합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="48" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>UE_CrusaderCriticalChain</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>성스러운 일격</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>기본 공격 치명타 시 {1}m 내 다른 적 최대 {0}명에게 공격력의 {2}% 전기 피해를 연쇄로 줍니다. 다음 대상마다 피해가 {3}%로 줄어듭니다. (쿨타임 {4}초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>UE_GuardiansJusticeShield</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>정의는 승리한다</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>피격으로 잃은 체력의 {0}%를 최대 체력의 {1}%까지 저장합니다. 첫 피격 후 {2}초 내 기본 공격 적중 시 {3}초 보호막으로 전환합니다. (쿨타임 {4}초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>UE_NinjaDodgeAttack</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>그림자 보법</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>회피 후 {1}초 내 다음 기본 공격의 피해가 {0}% 증가합니다. 빗나가도 소모됩니다. (쿨타임 {2}초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>UE_AntimatterPiercingShot</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>집속 사격</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>기본 사격이 최대 {0}명을 관통합니다. 두 번째·세 번째 적에게 기본 피해의 {1}%·{2}% 피해를 줍니다. 후속 피해는 치명타가 없으며 벽은 관통하지 못합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="48" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>UE_EchoVaultReplay</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>충격파 축적</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>산탄 발사 {0}초 후 같은 위치·방향에서 최대 {2}명에게 공격력의 {1}% 추가 피해를 줍니다. 치명타는 없으며 동시 최대 {4}회까지 예약합니다. (쿨타임 {3}초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>UE_WorldEnderChargedBlast</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>종말 포격</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>{0}초 충전 후 다음 유탄 충돌 시 반경 {1}m 내 최대 {3}명에게 공격력의 {2}% 추가 폭발 피해를 줍니다. 치명타는 없습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>UE_CoreBreakerArmorBreak</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>코어 노출</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>{1}초 내 같은 적에게 기본 공격을 {0}회 적중시키면 {2}초간 방어력을 {3}% 낮춥니다. 보스는 {4}% 감소하며 중첩되지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="48" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>UE_SuperRefrigerantFreeze</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>열 강탈</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>기본 공격 시 {2}초간 적의 이동 속도를 {3}%로 낮춥니다. {1}초 내 같은 적에게 {0}회 적중하면 {4}초간 빙결합니다. 대상별 빙결 쿨타임은 {5}초이며 보스는 감속만 적용합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="48" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>UE_WildfireSpread</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>되살아나는 불씨</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>이 무기의 화상이 남은 적 처치 시 {0}m 내 최대 {1}명에게 화상을 옮깁니다. 전파된 화상은 다시 전파되지 않습니다. (쿨타임 {2}초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="48" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>UE_SmileSignalMark</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>기분 전환</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>기본 사격 시 {0}초간 표식을 남깁니다. 아군의 다음 기본 공격이 표식을 소모해 공격자 공격력의 {1}% 추가 피해를 줍니다. 치명타는 없으며 혼자면 직접 소모합니다. 최대 {2}개, 재부여 대기시간은 {3}초입니다.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1910,7 +2104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3434,6 +3628,193 @@
       </c>
       <c r="C90" s="5" t="str">
         <v>Each distinct basic attack that hits builds 1 Heat, up to {0}. Once fully charged, the next valid basic hit consumes all Heat and deals non-critical Fire damage equal to {3}% of Attack Power to up to {4} enemies in a {1}m frontal cone with a total angle of {2}°. Heat expires after {5}s without a basic hit.</v>
+      </c>
+    </row>
+    <row r="91" ht="48" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>UE_SunfallBurnField</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Eclipse Ignition</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>Grenade impact leaves a {0} m burn field for {1} seconds. Refreshes the existing burn every {2} seconds; up to {3} fields per owner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="48" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>UE_CrusaderCriticalChain</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Holy Strike</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>A critical basic hit chains lightning to up to {0} other enemies within {1} m. First damage is {2}% attack power; each next jump uses {3}% of the previous multiplier. Cooldown: {4} seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>UE_GuardiansJusticeShield</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Justice Prevails</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>Stores {0}% of health actually lost to enemies, up to {1}% of maximum health. A basic hit within {2} seconds of the first loss converts it into a {3}-second shield. Cooldown: {4} seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>UE_NinjaDodgeAttack</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>Shadow Step</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>After dodging, adds {0}% to the next basic attack multiplier if executed within {1} seconds. Consumed even on a miss. Cooldown: {2} seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>UE_AntimatterPiercingShot</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Focused Fire</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Basic shots pierce up to {0} distinct enemies. The first takes normal damage; the second and third take noncritical effect damage at {1}% and {2}%. Walls stop the shot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="48" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>UE_EchoVaultReplay</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Shockwave Buildup</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>Replays the shotgun area from its original position and direction after {0} seconds, dealing {1}% attack power as noncritical damage to up to {2} enemies. Cooldown: {3} seconds; up to {4} pending replays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>UE_WorldEnderChargedBlast</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Doomsday Barrage</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>Readies a charged round every {0} seconds while equipped. The next grenade's first impact adds a {1} m blast dealing {2}% attack power as noncritical damage to up to {3} enemies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>UE_CoreBreakerArmorBreak</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>Core Exposure</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>Hit the same enemy with {0} distinct basic attacks within {1} seconds to reduce its defense by {3}% for {2} seconds, or {4}% against bosses. Does not stack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="48" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>UE_SuperRefrigerantFreeze</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>Heat Theft</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>Basic hits reduce movement speed to {3}% for {2} seconds. Hit the same enemy {0} times within {1} seconds to freeze it for {4} seconds. Each target has a {5}-second freeze lockout. Bosses are only slowed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="48" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>UE_WildfireSpread</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Rekindled Ember</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>Killing an enemy still burning from this weapon spreads its burn to up to {1} enemies within {0} m. Spread burns cannot spread again. Cooldown: {2} seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="48" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>UE_SmileSignalMark</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Mood Boost</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>Basic shots mark surviving enemies for {0} seconds. An ally's next basic hit consumes the mark for {1}% of that ally's attack power as noncritical extra damage. Up to {2} marks per owner; {3}-second target re-mark lockout. When alone, your next attack can consume it.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3447,7 +3828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4971,6 +5352,193 @@
       </c>
       <c r="C90" s="5" t="str">
         <v>異なる通常攻撃が命中するたびに熱を1蓄積し、最大{0}までチャージします。チャージ完了後の次の有効な通常攻撃で熱をすべて消費し、前方{1}m・全角{2}°内の敵最大{4}体に攻撃力の{3}%のクリティカルなしの炎ダメージを追加で与えます。通常攻撃が{5}秒間命中しないと熱が消失します。</v>
+      </c>
+    </row>
+    <row r="91" ht="48" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>UE_SunfallBurnField</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>日食点火</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>榴弾の着弾位置に半径{0}mの炎上地帯を{1}秒間残します。{2}秒ごとに既存の炎上を更新し、同時に最大{3}個まで維持します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="48" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>UE_CrusaderCriticalChain</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>聖なる一撃</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>通常攻撃のクリティカル時、半径{1}m以内の他の敵最大{0}体に電撃が連鎖します。初撃は攻撃力の{2}%、次の連鎖は直前の倍率の{3}%です。クールダウン{4}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>UE_GuardiansJusticeShield</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>正義は勝つ</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>敵による実際の体力損失の{0}%を最大体力の{1}%まで蓄積します。最初の損失から{2}秒以内に通常攻撃が命中すると、蓄積量を{3}秒間のシールドに変換します。クールダウン{4}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>UE_NinjaDodgeAttack</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>影の歩法</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>回避後{1}秒以内に実行した次の通常攻撃のダメージ倍率に{0}%を加算します。空振りでも消費します。クールダウン{2}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>UE_AntimatterPiercingShot</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>集束射撃</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>通常射撃が異なる敵を最大{0}体まで貫通します。最初は通常ダメージ、2体目と3体目にはそれぞれ{1}%、{2}%の非クリティカル効果ダメージを与えます。壁で止まります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="48" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>UE_EchoVaultReplay</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>衝撃波蓄積</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>散弾射撃の元の位置と方向から{0}秒後に範囲を再生し、最大{2}体に攻撃力の{1}%の非クリティカルダメージを与えます。クールダウン{3}秒、同時予約は最大{4}回。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>UE_WorldEnderChargedBlast</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>終末砲撃</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>装備後{0}秒ごとに強化弾を準備します。次の榴弾の最初の衝突時、半径{1}m内の最大{3}体に攻撃力の{2}%の非クリティカル追加爆発ダメージを与えます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>UE_CoreBreakerArmorBreak</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>コア露出</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>{1}秒以内に同じ敵へ異なる通常攻撃を{0}回命中させると、{2}秒間防御力を{3}%低下させます。ボスは{4}%低下し、重複しません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="48" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>UE_SuperRefrigerantFreeze</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>熱の強奪</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>通常攻撃で{2}秒間移動速度を元の{3}%にします。同じ敵に{1}秒以内に{0}回命中すると{4}秒間凍結します。対象ごとの凍結制限は{5}秒。ボスには減速のみ適用します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="48" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>UE_WildfireSpread</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>甦る残り火</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>この武器による自分の炎上が残っている敵を倒すと、半径{0}m内の最大{1}体に炎上を広げます。伝播した炎上は再伝播しません。クールダウン{2}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="48" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>UE_SmileSignalMark</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>気分転換</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>通常射撃で生き残った敵に{0}秒の印を付けます。味方の次の通常攻撃が印を消費し、その味方の攻撃力の{1}%の非クリティカル追加ダメージを与えます。所有者ごとに最大{2}個、対象の再付与制限は{3}秒。単独時は自分の次の攻撃で消費できます。</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4984,7 +5552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6510,6 +7078,193 @@
         <v>每次不同的普通攻击命中时积累1点热量，最多{0}点。充满后，下次有效普通攻击消耗全部热量，对前方{1}米、总夹角{2}°内最多{4}个敌人额外造成攻击力{3}%的无法暴击的火焰伤害。{5}秒内没有普通攻击命中时，热量清空。</v>
       </c>
     </row>
+    <row r="91" ht="48" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>UE_SunfallBurnField</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>日蚀点火</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>榴弹命中后留下半径{0}米、持续{1}秒的燃烧区域。每{2}秒刷新现有灼烧，每名玩家最多同时维持{3}个。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="48" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>UE_CrusaderCriticalChain</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>神圣一击</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr">
+        <is>
+          <t>普通攻击暴击后，闪电连锁攻击{1}米内最多{0}个其他敌人。首次伤害为攻击力的{2}%，后续倍率为上次的{3}%。冷却{4}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>UE_GuardiansJusticeShield</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>正义必胜</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>储存受到敌人攻击时实际损失生命的{0}%，上限为最大生命的{1}%。首次损失后{2}秒内普通攻击命中，将储存量转化为持续{3}秒的护盾。冷却{4}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>UE_NinjaDodgeAttack</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>暗影步法</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr">
+        <is>
+          <t>闪避后{1}秒内实际发动的下一次普通攻击，伤害倍率增加{0}%。未命中也会消耗。冷却{2}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>UE_AntimatterPiercingShot</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>集束射击</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>普通射击最多贯穿{0}个不同敌人。首个目标受到正常伤害，第二、第三个目标分别受到{1}%、{2}%的非暴击效果伤害。墙壁会阻挡子弹。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="48" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>UE_EchoVaultReplay</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>冲击波蓄积</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr">
+        <is>
+          <t>{0}秒后在原散弹射击位置与方向重现攻击范围，对最多{2}个敌人造成攻击力{1}%的非暴击伤害。冷却{3}秒，最多同时预约{4}次。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>UE_WorldEnderChargedBlast</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>末日炮击</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>装备后每{0}秒准备一发强化弹。下一枚榴弹首次碰撞时，额外爆炸对半径{1}米内最多{3}个敌人造成攻击力{2}%的非暴击伤害。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>UE_CoreBreakerArmorBreak</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>核心暴露</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr">
+        <is>
+          <t>{1}秒内以{0}次不同普通攻击命中同一敌人，使其防御降低{3}%，持续{2}秒。对首领降低{4}%，不可叠加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="48" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>UE_SuperRefrigerantFreeze</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>热量掠夺</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>普通攻击使移动速度降至原本的{3}%，持续{2}秒。{1}秒内命中同一敌人{0}次可冻结{4}秒。每个目标的冻结间隔为{5}秒。首领仅受减速影响。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="48" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>UE_WildfireSpread</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>复燃余烬</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr">
+        <is>
+          <t>击杀仍带有此武器施加的自身灼烧的敌人时，将灼烧传至{0}米内最多{1}个敌人。传播的灼烧不会再次传播。冷却{2}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="48" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>UE_SmileSignalMark</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>转换心情</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>普通射击为存活敌人留下{0}秒标记。队友下一次普通攻击消耗标记，造成该队友攻击力{1}%的非暴击额外伤害。每名拥有者最多{2}个标记，目标重新标记间隔为{3}秒。独自作战时可由自己的下一次攻击消耗。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>적을 처치할 때마다 공격력이 {0}% 증가합니다.</t>
+          <t>적을 처치할 때마다 공격력이 {0}% 증가합니다. 최대 100회 중첩되며 공격력은 최대 50% 증가합니다.</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>{1}초 내 같은 적에게 기본 공격을 {0}회 적중시키면 {2}초간 방어력을 {3}% 낮춥니다. 보스는 {4}% 감소하며 중첩되지 않습니다.</t>
+          <t>{1}초 내 같은 적에게 기본 공격을 {0}회 적중시키면 {2}초간 방어력을 {3}% 낮춥니다. 보스는 {4}% 감소하며 중첩되지 않습니다. 다른 적을 적중시키면 누적 적중 횟수가 초기화됩니다.</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>기본 공격 시 {2}초간 적의 이동 속도를 {3}%로 낮춥니다. {1}초 내 같은 적에게 {0}회 적중하면 {4}초간 빙결합니다. 대상별 빙결 쿨타임은 {5}초이며 보스는 감속만 적용합니다.</t>
+          <t>기본 공격 시 {2}초간 적의 이동 속도를 {3}%로 낮춥니다. {1}초 내 같은 적에게 {0}회 적중하면 {4}초간 빙결합니다. 대상별 빙결 쿨타임은 {5}초이며 보스는 감속만 적용합니다. 다른 적을 적중시키면 누적 적중 횟수가 초기화됩니다.</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Each time you defeat an enemy, Attack increases by {0}%.</t>
+          <t>Each time you defeat an enemy, Attack increases by {0}%. Stacks up to 100 times, for a maximum Attack increase of 50%.</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>Hit the same enemy with {0} distinct basic attacks within {1} seconds to reduce its defense by {3}% for {2} seconds, or {4}% against bosses. Does not stack.</t>
+          <t>Hit the same enemy with {0} distinct basic attacks within {1} seconds to reduce its defense by {3}% for {2} seconds, or {4}% against bosses. Does not stack. Hitting a different enemy resets the accumulated hit count.</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>Basic hits reduce movement speed to {3}% for {2} seconds. Hit the same enemy {0} times within {1} seconds to freeze it for {4} seconds. Each target has a {5}-second freeze lockout. Bosses are only slowed.</t>
+          <t>Basic hits reduce movement speed to {3}% for {2} seconds. Hit the same enemy {0} times within {1} seconds to freeze it for {4} seconds. Each target has a {5}-second freeze lockout. Bosses are only slowed. Hitting a different enemy resets the accumulated hit count.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>敵を倒すたびに、攻撃力が{0}%増加します。</t>
+          <t>敵を倒すたびに、攻撃力が{0}%増加します。 最大100回まで重複し、攻撃力は最大50%増加します。</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>{1}秒以内に同じ敵へ異なる通常攻撃を{0}回命中させると、{2}秒間防御力を{3}%低下させます。ボスは{4}%低下し、重複しません。</t>
+          <t>{1}秒以内に同じ敵へ異なる通常攻撃を{0}回命中させると、{2}秒間防御力を{3}%低下させます。ボスは{4}%低下し、重複しません。 別の敵に命中すると、累積命中回数がリセットされます。</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>通常攻撃で{2}秒間移動速度を元の{3}%にします。同じ敵に{1}秒以内に{0}回命中すると{4}秒間凍結します。対象ごとの凍結制限は{5}秒。ボスには減速のみ適用します。</t>
+          <t>通常攻撃で{2}秒間移動速度を元の{3}%にします。同じ敵に{1}秒以内に{0}回命中すると{4}秒間凍結します。対象ごとの凍結制限は{5}秒。ボスには減速のみ適用します。 別の敵に命中すると、累積命中回数がリセットされます。</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>每击败一个敌人，攻击力提高{0}%。</t>
+          <t>每击败一个敌人，攻击力提高{0}%。 最多叠加100层，攻击力最多提高50%。</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>{1}秒内以{0}次不同普通攻击命中同一敌人，使其防御降低{3}%，持续{2}秒。对首领降低{4}%，不可叠加。</t>
+          <t>{1}秒内以{0}次不同普通攻击命中同一敌人，使其防御降低{3}%，持续{2}秒。对首领降低{4}%，不可叠加。 命中其他敌人时，累计命中次数会重置。</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>普通攻击使移动速度降至原本的{3}%，持续{2}秒。{1}秒内命中同一敌人{0}次可冻结{4}秒。每个目标的冻结间隔为{5}秒。首领仅受减速影响。</t>
+          <t>普通攻击使移动速度降至原本的{3}%，持续{2}秒。{1}秒内命中同一敌人{0}次可冻结{4}秒。每个目标的冻结间隔为{5}秒。首领仅受减速影响。 命中其他敌人时，累计命中次数会重置。</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -65,20 +65,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -376,7 +376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -407,12 +407,12 @@
           <t>UE_QuantumShoes</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>퀀텀 부스트</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>이동 속도가 {0:F1} 증가합니다.</t>
         </is>
@@ -424,12 +424,12 @@
           <t>UE_MassProducedCore</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>쾌속 발놀림</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>기본 공격 적중 시 {0}초간 이동 속도가 {1}% 증가합니다.</t>
         </is>
@@ -441,12 +441,12 @@
           <t>UE_SturdyArmor</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>사력을 다한 질주</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>체력이 {0}% 이하로 떨어지면 이동 속도가 {1}% 증가합니다. 다시 넘어서면 해제됩니다.</t>
         </is>
@@ -458,12 +458,12 @@
           <t>UE_AdvancedCore</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>증강</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>최대 체력이 {0} 증가합니다.</t>
         </is>
@@ -475,12 +475,12 @@
           <t>UE_CyberneticCore</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>기초적인 임플란트</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>회피 사용 시 신경 가속 모드에 들어갑니다. {0}초 동안 이동 속도가 {1} 증가합니다. (쿨타임 {2}초)</t>
         </is>
@@ -504,68 +504,68 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>UE_MechanicalDestroyer</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>공격 강화</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>장착 중 공격력이 {0}% 증가합니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>UE_HeartOfDebris</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>데브리스의 맥동</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>체력이 {0}% 이하로 떨어지면 공격력이 {1}% 증가합니다. 다시 넘어서면 해제됩니다.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>UE_OverclockCore</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>오버클럭</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>공격력이 {0}% 증가, 체력이 {1}% 감소합니다.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>UE_ScrapCompactor</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>잔해 압축</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>적을 처치할 때마다 공격력이 {0}% 증가합니다. 최대 100회 중첩되며 공격력은 최대 50% 증가합니다.</t>
         </is>
@@ -1863,44 +1863,52 @@
         </is>
       </c>
     </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="88" ht="26.399999618530273" customHeight="1">
-      <c r="A88" t="inlineStr" s="4">
+    <row r="88" ht="26.39999961853027" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>UE_PhaseHarvesterWave</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr" s="4">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>공허 처형 파동</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr" s="5">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>근접 기본 공격으로 처치 시 전방 {0}m·폭 {1}m의 파동을 방출합니다. 최대 {3}명에게 공격력의 {2}% 무속성 피해를 주며 치명타는 없습니다. (쿨타임 {4}초)</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="26.399999618530273" customHeight="1">
-      <c r="A89" t="str" s="4">
-        <v>UE_StarforgeBreachExplosion</v>
-      </c>
-      <c r="B89" t="str" s="6">
-        <v>스타 브리처 근접 폭발</v>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
+    <row r="89" ht="26.39999961853027" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>UE_StarforgeBreachExplosion</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>스타 브리처 근접 폭발</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>{0}m 이내 산탄 적중 시 반경 {1}m에 폭발을 일으킵니다. 최대 {3}명에게 공격력의 {2}% 화염 피해를 주며 치명타는 없습니다. (쿨타임 {4}초)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="39.599998474121094" customHeight="1">
-      <c r="A90" s="4" t="str">
-        <v>UE_WasteHeatDischarge</v>
-      </c>
-      <c r="B90" s="6" t="str">
-        <v>폐열 방출</v>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
+    <row r="90" ht="39.59999847412109" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>UE_WasteHeatDischarge</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>폐열 방출</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>기본 공격 {0}회 적중 후 다음 적중 시 화염을 방출합니다. 전방 {1}m·{2}° 내 최대 {4}명에게 공격력의 {3}% 추가 피해를 줍니다. 치명타는 없으며 {5}초간 미적중 시 충전이 초기화됩니다.</t>
         </is>
@@ -1912,7 +1920,7 @@
           <t>UE_SunfallBurnField</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>일식 점화</t>
         </is>
@@ -1929,7 +1937,7 @@
           <t>UE_CrusaderCriticalChain</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>성스러운 일격</t>
         </is>
@@ -1946,7 +1954,7 @@
           <t>UE_GuardiansJusticeShield</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>정의는 승리한다</t>
         </is>
@@ -1963,7 +1971,7 @@
           <t>UE_NinjaDodgeAttack</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>그림자 보법</t>
         </is>
@@ -1980,7 +1988,7 @@
           <t>UE_AntimatterPiercingShot</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>집속 사격</t>
         </is>
@@ -1997,7 +2005,7 @@
           <t>UE_EchoVaultReplay</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>충격파 축적</t>
         </is>
@@ -2014,7 +2022,7 @@
           <t>UE_WorldEnderChargedBlast</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>종말 포격</t>
         </is>
@@ -2031,7 +2039,7 @@
           <t>UE_CoreBreakerArmorBreak</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>코어 노출</t>
         </is>
@@ -2048,7 +2056,7 @@
           <t>UE_SuperRefrigerantFreeze</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>열 강탈</t>
         </is>
@@ -2065,7 +2073,7 @@
           <t>UE_WildfireSpread</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>되살아나는 불씨</t>
         </is>
@@ -2082,7 +2090,7 @@
           <t>UE_SmileSignalMark</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>기분 전환</t>
         </is>
@@ -2090,6 +2098,278 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>기본 사격 시 {0}초간 표식을 남깁니다. 아군의 다음 기본 공격이 표식을 소모해 공격자 공격력의 {1}% 추가 피해를 줍니다. 치명타는 없으며 혼자면 직접 소모합니다. 최대 {2}개, 재부여 대기시간은 {3}초입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>UE_RailSweep</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>레일 소인</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>1번 스킬 시전 시 {0}초간 일반 공격 피해가 {1}%, 공격 속도가 {2}% 증가합니다. (쿨타임 {3}초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>UE_PileDriverQuake</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>진동 누적</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>스킬 적중 시 {0}초간 스킬 피해가 {1}% 증가합니다. (최대 {2}스택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>UE_DampingCore</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>감쇠 증폭</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>스킬 피해가 {0}% 증가하지만 마나 재생이 {1}% 감소합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>UE_IceRush</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>빙결 돌입</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>회피(대시 포함) 후 다음 기본 공격의 피해가 {0}% 증가합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>UE_OverloadHeart</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>과부하 순환</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>적 처치 시 {0}번 스킬의 남은 쿨타임이 {1}초 감소합니다. (내부 쿨타임 0.5초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>UE_AdrenalineInjector</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>과잉 분비</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>스킬 쿨타임이 {0}% 감소하지만 최대 체력이 {1}% 감소합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>UE_NovaCapacitor</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>대용량 축전</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>최대 마나가 {0}, 마나 재생이 {1}% 증가합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>UE_ChargeCircuit</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>회로 재충전</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>적 처치 시 {0}번 스킬의 충전이 {1}초 진행됩니다. (내부 쿨타임 1초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>UE_HaloShrapnel</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>냉각 파편</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>스킬 적중 시 {0}초간 빙결 피해 보너스가 {1} 증가합니다. 기본 공격에도 적용됩니다. (최대 {2}스택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>UE_RecoilStep</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>반동 회피</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>회피(백스탭 포함) 시 {0}초간 공격 속도가 {1}%, 일반 공격 피해가 {2}% 증가합니다. (쿨타임 {3}초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>UE_TargetLens</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>약점 분석</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>표식이 걸린 적에게 주는 피해가 {0}% 증가합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>UE_ManaConverter</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>변환 출력</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>스킬 시전 시 {0}초간 일반 공격 피해가 {1}% 증가합니다. (최대 {2}스택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>UE_SpareBattery</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>예비 전력</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>최대 마나가 {0} 증가합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>UE_CoolantArmor</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>냉각 순환</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>스킬 적중 시 {0}초간 마나 재생이 {1}% 증가합니다. (쿨타임 {2}초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>UE_HeatExchanger</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>열교환</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>화염·빙결·전기 피해 보너스가 각각 {0}, 스킬 피해가 {1}% 증가합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>UE_ElementResonator</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>과부하</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>화상·빙결·감전 중 서로 다른 두 가지가 걸린 적을 적중하면 반경 {0}m에 공격력 {1}%의 무속성 폭발을 일으킵니다. (대상별 {2}초, 최대 {3}명)</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2232,7 +2512,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>UE_MechanicalDestroyer</t>
         </is>
@@ -2249,7 +2529,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>UE_HeartOfDebris</t>
         </is>
@@ -2266,7 +2546,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>UE_OverclockCore</t>
         </is>
@@ -2283,7 +2563,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>UE_ScrapCompactor</t>
         </is>
@@ -3591,43 +3871,55 @@
         </is>
       </c>
     </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="88" ht="52.79999923706055" customHeight="1">
-      <c r="A88" t="inlineStr" s="4">
+    <row r="88" ht="52.79999923706055" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>UE_PhaseHarvesterWave</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr" s="4">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>Void Execution Wave</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr" s="5">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>When a Fighter basic attack kills an enemy, an execution wave instantly covers a {0}m-long, {1}m-wide corridor ahead of the kill position. It deals {2}% non-elemental damage once to up to {3} living enemies, without critical hits or repeated activation. Cooldown: {4}s.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="39.599998474121094" customHeight="1">
-      <c r="A89" t="str" s="4">
-        <v>UE_StarforgeBreachExplosion</v>
-      </c>
-      <c r="B89" t="str" s="6">
-        <v>Star Breacher Close-Range Explosion</v>
-      </c>
-      <c r="C89" s="5" t="str">
-        <v>A Gunner basic shotgun hit within {0}m of the firing origin causes an explosion of radius {1}m at the impact point. It deals {2}% Fire damage once to up to {3} enemies, without critical hits. Cooldown: {4}s.</v>
+    <row r="89" ht="39.59999847412109" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>UE_StarforgeBreachExplosion</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Star Breacher Close-Range Explosion</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>A Gunner basic shotgun hit within {0}m of the firing origin causes an explosion of radius {1}m at the impact point. It deals {2}% Fire damage once to up to {3} enemies, without critical hits. Cooldown: {4}s.</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="52.79999923706055" customHeight="1">
-      <c r="A90" s="4" t="str">
-        <v>UE_WasteHeatDischarge</v>
-      </c>
-      <c r="B90" s="6" t="str">
-        <v>Waste Heat Discharge</v>
-      </c>
-      <c r="C90" s="5" t="str">
-        <v>Each distinct basic attack that hits builds 1 Heat, up to {0}. Once fully charged, the next valid basic hit consumes all Heat and deals non-critical Fire damage equal to {3}% of Attack Power to up to {4} enemies in a {1}m frontal cone with a total angle of {2}°. Heat expires after {5}s without a basic hit.</v>
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>UE_WasteHeatDischarge</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Waste Heat Discharge</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Each distinct basic attack that hits builds 1 Heat, up to {0}. Once fully charged, the next valid basic hit consumes all Heat and deals non-critical Fire damage equal to {3}% of Attack Power to up to {4} enemies in a {1}m frontal cone with a total angle of {2}°. Heat expires after {5}s without a basic hit.</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1">
@@ -3636,7 +3928,7 @@
           <t>UE_SunfallBurnField</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>Eclipse Ignition</t>
         </is>
@@ -3653,7 +3945,7 @@
           <t>UE_CrusaderCriticalChain</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>Holy Strike</t>
         </is>
@@ -3670,7 +3962,7 @@
           <t>UE_GuardiansJusticeShield</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>Justice Prevails</t>
         </is>
@@ -3687,7 +3979,7 @@
           <t>UE_NinjaDodgeAttack</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>Shadow Step</t>
         </is>
@@ -3704,7 +3996,7 @@
           <t>UE_AntimatterPiercingShot</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Focused Fire</t>
         </is>
@@ -3721,7 +4013,7 @@
           <t>UE_EchoVaultReplay</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>Shockwave Buildup</t>
         </is>
@@ -3738,7 +4030,7 @@
           <t>UE_WorldEnderChargedBlast</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>Doomsday Barrage</t>
         </is>
@@ -3755,7 +4047,7 @@
           <t>UE_CoreBreakerArmorBreak</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>Core Exposure</t>
         </is>
@@ -3772,7 +4064,7 @@
           <t>UE_SuperRefrigerantFreeze</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>Heat Theft</t>
         </is>
@@ -3789,7 +4081,7 @@
           <t>UE_WildfireSpread</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>Rekindled Ember</t>
         </is>
@@ -3806,7 +4098,7 @@
           <t>UE_SmileSignalMark</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>Mood Boost</t>
         </is>
@@ -3814,6 +4106,278 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>Basic shots mark surviving enemies for {0} seconds. An ally's next basic hit consumes the mark for {1}% of that ally's attack power as noncritical extra damage. Up to {2} marks per owner; {3}-second target re-mark lockout. When alone, your next attack can consume it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>UE_RailSweep</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Rail Sweep</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Casting skill 1 increases basic attack damage by {1}% and Attack Speed by {2}% for {0} seconds. (Cooldown {3}s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>UE_PileDriverQuake</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Tremor Buildup</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Skill hits increase skill damage by {1}% for {0} seconds. (Up to {2} stacks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>UE_DampingCore</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Damping Amplifier</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Skill damage increases by {0}%, but Mana Regen decreases by {1}%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>UE_IceRush</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Frost Rush</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>After a dodge (including dash), your next basic attack deals {0}% more damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>UE_OverloadHeart</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Overload Cycle</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Defeating an enemy reduces skill {0}'s remaining cooldown by {1}s. (Internal cooldown 0.5s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>UE_AdrenalineInjector</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Overflow Secretion</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Skill cooldowns are reduced by {0}%, but Max HP decreases by {1}%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>UE_NovaCapacitor</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Mass Capacitor</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Max Mana increases by {0} and Mana Regen by {1}%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>UE_ChargeCircuit</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Circuit Recharge</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Defeating an enemy advances skill {0}'s charge by {1}s. (Internal cooldown 1s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>UE_HaloShrapnel</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Chilled Shrapnel</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Skill hits increase Ice damage bonus by {1} for {0} seconds. Also applies to basic attacks. (Up to {2} stacks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>UE_RecoilStep</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Recoil Step</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Dodging (including backstep) increases Attack Speed by {1}% and basic attack damage by {2}% for {0} seconds. (Cooldown {3}s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>UE_TargetLens</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Weakpoint Analysis</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Damage dealt to Marked enemies increases by {0}%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>UE_ManaConverter</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Converted Output</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Casting a skill increases basic attack damage by {1}% for {0} seconds. (Up to {2} stacks)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>UE_SpareBattery</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Reserve Power</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Max Mana increases by {0}.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>UE_CoolantArmor</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Coolant Cycle</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Skill hits increase Mana Regen by {1}% for {0} seconds. (Cooldown {2}s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>UE_HeatExchanger</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Heat Exchange</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Fire, Ice and Electric damage bonuses each increase by {0}, and skill damage by {1}%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>UE_ElementResonator</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Overload</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Hitting an enemy afflicted by two different elements (Burn, Freeze, Shock) triggers a non-elemental explosion dealing {1}% Attack within {0}m. ({2}s per target, up to {3} enemies)</t>
         </is>
       </c>
     </row>
@@ -3828,7 +4392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3956,7 +4520,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>UE_MechanicalDestroyer</t>
         </is>
@@ -3973,7 +4537,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>UE_HeartOfDebris</t>
         </is>
@@ -3990,7 +4554,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>UE_OverclockCore</t>
         </is>
@@ -4007,7 +4571,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>UE_ScrapCompactor</t>
         </is>
@@ -5315,43 +5879,55 @@
         </is>
       </c>
     </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="88" ht="39.599998474121094" customHeight="1">
-      <c r="A88" t="inlineStr" s="4">
+    <row r="88" ht="39.59999847412109" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>UE_PhaseHarvesterWave</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr" s="4">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>虚空の処刑波</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr" s="5">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>ファイターの通常攻撃で敵を倒すと、その位置から前方{0}m、幅{1}mの処刑波が即座に発生します。生存する最大{3}体に無属性ダメージ{2}%を1回与えます。クリティカルや連鎖発動は発生しません。クールダウンは{4}秒です。</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="39.599998474121094" customHeight="1">
-      <c r="A89" t="str" s="4">
-        <v>UE_StarforgeBreachExplosion</v>
-      </c>
-      <c r="B89" t="str" s="6">
-        <v>スターブリーチャー近距離爆発</v>
-      </c>
-      <c r="C89" s="5" t="str">
-        <v>ガンナーの通常ショットガン攻撃が発射位置から{0}m以内の敵に命中すると、命中位置に半径{1}mの爆発を起こします。最大{3}体にクリティカルなしの火炎ダメージ{2}%を1回与えます。クールダウン：{4}秒。</v>
+    <row r="89" ht="39.59999847412109" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>UE_StarforgeBreachExplosion</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>スターブリーチャー近距離爆発</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>ガンナーの通常ショットガン攻撃が発射位置から{0}m以内の敵に命中すると、命中位置に半径{1}mの爆発を起こします。最大{3}体にクリティカルなしの火炎ダメージ{2}%を1回与えます。クールダウン：{4}秒。</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="52.79999923706055" customHeight="1">
-      <c r="A90" s="4" t="str">
-        <v>UE_WasteHeatDischarge</v>
-      </c>
-      <c r="B90" s="6" t="str">
-        <v>廃熱放出</v>
-      </c>
-      <c r="C90" s="5" t="str">
-        <v>異なる通常攻撃が命中するたびに熱を1蓄積し、最大{0}までチャージします。チャージ完了後の次の有効な通常攻撃で熱をすべて消費し、前方{1}m・全角{2}°内の敵最大{4}体に攻撃力の{3}%のクリティカルなしの炎ダメージを追加で与えます。通常攻撃が{5}秒間命中しないと熱が消失します。</v>
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>UE_WasteHeatDischarge</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>廃熱放出</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>異なる通常攻撃が命中するたびに熱を1蓄積し、最大{0}までチャージします。チャージ完了後の次の有効な通常攻撃で熱をすべて消費し、前方{1}m・全角{2}°内の敵最大{4}体に攻撃力の{3}%のクリティカルなしの炎ダメージを追加で与えます。通常攻撃が{5}秒間命中しないと熱が消失します。</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1">
@@ -5360,7 +5936,7 @@
           <t>UE_SunfallBurnField</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>日食点火</t>
         </is>
@@ -5377,7 +5953,7 @@
           <t>UE_CrusaderCriticalChain</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>聖なる一撃</t>
         </is>
@@ -5394,7 +5970,7 @@
           <t>UE_GuardiansJusticeShield</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>正義は勝つ</t>
         </is>
@@ -5411,7 +5987,7 @@
           <t>UE_NinjaDodgeAttack</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>影の歩法</t>
         </is>
@@ -5428,7 +6004,7 @@
           <t>UE_AntimatterPiercingShot</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>集束射撃</t>
         </is>
@@ -5445,7 +6021,7 @@
           <t>UE_EchoVaultReplay</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>衝撃波蓄積</t>
         </is>
@@ -5462,7 +6038,7 @@
           <t>UE_WorldEnderChargedBlast</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>終末砲撃</t>
         </is>
@@ -5479,7 +6055,7 @@
           <t>UE_CoreBreakerArmorBreak</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>コア露出</t>
         </is>
@@ -5496,7 +6072,7 @@
           <t>UE_SuperRefrigerantFreeze</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>熱の強奪</t>
         </is>
@@ -5513,7 +6089,7 @@
           <t>UE_WildfireSpread</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>甦る残り火</t>
         </is>
@@ -5530,7 +6106,7 @@
           <t>UE_SmileSignalMark</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>気分転換</t>
         </is>
@@ -5538,6 +6114,278 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>通常射撃で生き残った敵に{0}秒の印を付けます。味方の次の通常攻撃が印を消費し、その味方の攻撃力の{1}%の非クリティカル追加ダメージを与えます。所有者ごとに最大{2}個、対象の再付与制限は{3}秒。単独時は自分の次の攻撃で消費できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>UE_RailSweep</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>レールスイープ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>スキル1の発動時、{0}秒間通常攻撃ダメージが{1}%、攻撃速度が{2}%増加します。（クールタイム{3}秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>UE_PileDriverQuake</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>振動蓄積</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>スキル命中時、{0}秒間スキルダメージが{1}%増加します。（最大{2}スタック）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>UE_DampingCore</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>減衰増幅</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>スキルダメージが{0}%増加しますが、マナ回復が{1}%減少します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>UE_IceRush</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>氷結突入</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>回避（ダッシュ含む）後、次の通常攻撃のダメージが{0}%増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>UE_OverloadHeart</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>過負荷循環</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>敵を倒すとスキル{0}の残りクールタイムが{1}秒短縮されます。（内部クールタイム0.5秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>UE_AdrenalineInjector</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>過剰分泌</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>スキルクールタイムが{0}%短縮されますが、最大HPが{1}%減少します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>UE_NovaCapacitor</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>大容量蓄電</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>最大マナが{0}、マナ回復が{1}%増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>UE_ChargeCircuit</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>回路再充電</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>敵を倒すとスキル{0}のチャージが{1}秒進みます。（内部クールタイム1秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>UE_HaloShrapnel</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>冷却破片</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>スキル命中時、{0}秒間氷結ダメージボーナスが{1}上昇します。通常攻撃にも適用されます。（最大{2}スタック）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>UE_RecoilStep</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>反動回避</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>回避（バックステップ含む）時、{0}秒間攻撃速度が{1}%、通常攻撃ダメージが{2}%増加します。（クールタイム{3}秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>UE_TargetLens</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>弱点分析</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>マーキングされた敵へのダメージが{0}%増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>UE_ManaConverter</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>変換出力</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>スキル発動時、{0}秒間通常攻撃ダメージが{1}%増加します。（最大{2}スタック）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>UE_SpareBattery</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>予備電力</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>最大マナが{0}増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>UE_CoolantArmor</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>冷却循環</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>スキル命中時、{0}秒間マナ回復が{1}%増加します。（クールタイム{2}秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>UE_HeatExchanger</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>熱交換</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>火炎・氷結・電気ダメージボーナスがそれぞれ{0}、スキルダメージが{1}%上昇します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>UE_ElementResonator</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>過負荷</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>火傷・凍結・感電のうち異なる2種類がかかった敵に命中すると、半径{0}mに攻撃力{1}%の無属性爆発を起こします。（対象ごと{2}秒、最大{3}体）</t>
         </is>
       </c>
     </row>
@@ -5552,7 +6400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5680,7 +6528,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>UE_MechanicalDestroyer</t>
         </is>
@@ -5697,7 +6545,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>UE_HeartOfDebris</t>
         </is>
@@ -5714,7 +6562,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>UE_OverclockCore</t>
         </is>
@@ -5731,7 +6579,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>UE_ScrapCompactor</t>
         </is>
@@ -7039,43 +7887,55 @@
         </is>
       </c>
     </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="88" ht="39.599998474121094" customHeight="1">
-      <c r="A88" t="inlineStr" s="4">
+    <row r="88" ht="39.59999847412109" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>UE_PhaseHarvesterWave</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr" s="4">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>虚空处决波</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr" s="5">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>斗士普通攻击击杀敌人后，立即从击杀位置向前形成长{0}米、宽{1}米的处决通道。对最多{3}个存活敌人各造成一次{2}%无属性伤害，不会暴击或连锁触发。冷却时间为{4}秒。</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="26.399999618530273" customHeight="1">
-      <c r="A89" t="str" s="4">
-        <v>UE_StarforgeBreachExplosion</v>
-      </c>
-      <c r="B89" t="str" s="6">
-        <v>星辰破阵者近距离爆炸</v>
-      </c>
-      <c r="C89" s="5" t="str">
-        <v>枪手的普通霰弹枪攻击命中距发射位置{0}m以内的敌人时，在命中位置引发半径{1}m的爆炸。对最多{3}个敌人造成一次{2}%火焰伤害，不会暴击。冷却时间：{4}秒。</v>
-      </c>
-    </row>
-    <row r="90" ht="39.599998474121094" customHeight="1">
-      <c r="A90" s="4" t="str">
-        <v>UE_WasteHeatDischarge</v>
-      </c>
-      <c r="B90" s="6" t="str">
-        <v>废热释放</v>
-      </c>
-      <c r="C90" s="5" t="str">
-        <v>每次不同的普通攻击命中时积累1点热量，最多{0}点。充满后，下次有效普通攻击消耗全部热量，对前方{1}米、总夹角{2}°内最多{4}个敌人额外造成攻击力{3}%的无法暴击的火焰伤害。{5}秒内没有普通攻击命中时，热量清空。</v>
+    <row r="89" ht="26.39999961853027" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>UE_StarforgeBreachExplosion</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>星辰破阵者近距离爆炸</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>枪手的普通霰弹枪攻击命中距发射位置{0}m以内的敌人时，在命中位置引发半径{1}m的爆炸。对最多{3}个敌人造成一次{2}%火焰伤害，不会暴击。冷却时间：{4}秒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="39.59999847412109" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>UE_WasteHeatDischarge</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>废热释放</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>每次不同的普通攻击命中时积累1点热量，最多{0}点。充满后，下次有效普通攻击消耗全部热量，对前方{1}米、总夹角{2}°内最多{4}个敌人额外造成攻击力{3}%的无法暴击的火焰伤害。{5}秒内没有普通攻击命中时，热量清空。</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="48" customHeight="1">
@@ -7084,7 +7944,7 @@
           <t>UE_SunfallBurnField</t>
         </is>
       </c>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>日蚀点火</t>
         </is>
@@ -7101,7 +7961,7 @@
           <t>UE_CrusaderCriticalChain</t>
         </is>
       </c>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>神圣一击</t>
         </is>
@@ -7118,7 +7978,7 @@
           <t>UE_GuardiansJusticeShield</t>
         </is>
       </c>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>正义必胜</t>
         </is>
@@ -7135,7 +7995,7 @@
           <t>UE_NinjaDodgeAttack</t>
         </is>
       </c>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>暗影步法</t>
         </is>
@@ -7152,7 +8012,7 @@
           <t>UE_AntimatterPiercingShot</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>集束射击</t>
         </is>
@@ -7169,7 +8029,7 @@
           <t>UE_EchoVaultReplay</t>
         </is>
       </c>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>冲击波蓄积</t>
         </is>
@@ -7186,7 +8046,7 @@
           <t>UE_WorldEnderChargedBlast</t>
         </is>
       </c>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>末日炮击</t>
         </is>
@@ -7203,7 +8063,7 @@
           <t>UE_CoreBreakerArmorBreak</t>
         </is>
       </c>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>核心暴露</t>
         </is>
@@ -7220,7 +8080,7 @@
           <t>UE_SuperRefrigerantFreeze</t>
         </is>
       </c>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>热量掠夺</t>
         </is>
@@ -7237,7 +8097,7 @@
           <t>UE_WildfireSpread</t>
         </is>
       </c>
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>复燃余烬</t>
         </is>
@@ -7254,7 +8114,7 @@
           <t>UE_SmileSignalMark</t>
         </is>
       </c>
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>转换心情</t>
         </is>
@@ -7262,6 +8122,278 @@
       <c r="C101" s="7" t="inlineStr">
         <is>
           <t>普通射击为存活敌人留下{0}秒标记。队友下一次普通攻击消耗标记，造成该队友攻击力{1}%的非暴击额外伤害。每名拥有者最多{2}个标记，目标重新标记间隔为{3}秒。独自作战时可由自己的下一次攻击消耗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>UE_RailSweep</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>磁轨横扫</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>施放1号技能时，{0}秒内普通攻击伤害提高{1}%，攻击速度提高{2}%。（冷却{3}秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>UE_PileDriverQuake</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>震动累积</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>技能命中时，{0}秒内技能伤害提高{1}%。（最多{2}层）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>UE_DampingCore</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>阻尼增幅</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>技能伤害提高{0}%，但法力恢复降低{1}%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>UE_IceRush</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>冰结突进</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>闪避（含冲刺）后，下一次普通攻击伤害提高{0}%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>UE_OverloadHeart</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>过载循环</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>击败敌人时，{0}号技能的剩余冷却减少{1}秒。（内部冷却0.5秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>UE_AdrenalineInjector</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>过量分泌</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>技能冷却缩短{0}%，但最大生命值降低{1}%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>UE_NovaCapacitor</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>大容量蓄电</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>最大法力提高{0}，法力恢复提高{1}%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>UE_ChargeCircuit</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>回路充能</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>击败敌人时，{0}号技能的充能推进{1}秒。（内部冷却1秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>UE_HaloShrapnel</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>冷却碎片</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>技能命中时，{0}秒内冰结伤害加成提高{1}，普通攻击同样适用。（最多{2}层）</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>UE_RecoilStep</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>后坐闪避</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>闪避（含后撤步）时，{0}秒内攻击速度提高{1}%，普通攻击伤害提高{2}%。（冷却{3}秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>UE_TargetLens</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>弱点分析</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>对带有标记的敌人造成的伤害提高{0}%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>UE_ManaConverter</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>转换输出</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>施放技能时，{0}秒内普通攻击伤害提高{1}%。（最多{2}层）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>UE_SpareBattery</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>备用电力</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>最大法力提高{0}。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>UE_CoolantArmor</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>冷却循环</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>技能命中时，{0}秒内法力恢复提高{1}%。（冷却{2}秒）</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>UE_HeatExchanger</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>热交换</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>火焰、冰结、电击伤害加成各提高{0}，技能伤害提高{1}%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>UE_ElementResonator</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>过载</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>命中同时处于灼烧、冰冻、感电中任意两种不同状态的敌人时，在半径{0}米内引发攻击力{1}%的无属性爆炸。（每个目标{2}秒，最多{3}名）</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectLabel.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>적을 처치할 때마다 공격력이 {0}% 증가합니다. 최대 100회 중첩되며 공격력은 최대 50% 증가합니다.</t>
+          <t>적을 처치할 때마다 공격력이 {0}% 증가합니다. 최대 40회 중첩되며 공격력은 최대 20% 증가합니다.</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>화상·빙결·감전 중 서로 다른 두 가지가 걸린 적을 적중하면 반경 {0}m에 공격력 {1}%의 무속성 폭발을 일으킵니다. (대상별 {2}초, 최대 {3}명)</t>
+          <t>화상·빙결·감전 중 하나라도 걸린 적을 적중하면 반경 {0}m에 공격력 {1}%의 무속성 폭발을 일으킵니다. 서로 다른 두 가지가 걸려 있으면 폭발 피해가 50% 증가합니다. (대상별 {2}초, 최대 {3}명)</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Each time you defeat an enemy, Attack increases by {0}%. Stacks up to 100 times, for a maximum Attack increase of 50%.</t>
+          <t>Each time you defeat an enemy, Attack increases by {0}%. Stacks up to 40 times, for a maximum Attack increase of 20%.</t>
         </is>
       </c>
     </row>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hitting an enemy afflicted by two different elements (Burn, Freeze, Shock) triggers a non-elemental explosion dealing {1}% Attack within {0}m. ({2}s per target, up to {3} enemies)</t>
+          <t>Hitting an enemy afflicted by Burn, Freeze, or Shock triggers a non-elemental explosion dealing {1}% Attack within {0}m. The explosion deals 50% more damage if the enemy has two different elements. ({2}s per target, up to {3} enemies)</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>敵を倒すたびに、攻撃力が{0}%増加します。 最大100回まで重複し、攻撃力は最大50%増加します。</t>
+          <t>敵を倒すたびに、攻撃力が{0}%増加します。 最大40回まで重複し、攻撃力は最大20%増加します。</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>火傷・凍結・感電のうち異なる2種類がかかった敵に命中すると、半径{0}mに攻撃力{1}%の無属性爆発を起こします。（対象ごと{2}秒、最大{3}体）</t>
+          <t>火傷・凍結・感電のいずれかがかかった敵に命中すると、半径{0}mに攻撃力{1}%の無属性爆発を起こします。異なる2種類がかかっている場合、爆発ダメージが50%増加します。（対象ごと{2}秒、最大{3}体）</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>每击败一个敌人，攻击力提高{0}%。 最多叠加100层，攻击力最多提高50%。</t>
+          <t>每击败一个敌人，攻击力提高{0}%。 最多叠加40层，攻击力最多提高20%。</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>命中同时处于灼烧、冰冻、感电中任意两种不同状态的敌人时，在半径{0}米内引发攻击力{1}%的无属性爆炸。（每个目标{2}秒，最多{3}名）</t>
+          <t>命中处于灼烧、冰冻、感电中任意一种状态的敌人时，在半径{0}米内引发攻击力{1}%的无属性爆炸。若同时处于两种不同状态，爆炸伤害提高50%。（每个目标{2}秒，最多{3}名）</t>
         </is>
       </c>
     </row>
